--- a/Outputs/Scenarios/PtX_demand_MT_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_MT_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.000642864351279804</v>
+        <v>0.0003484563351089362</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.000214288117093268</v>
+        <v>0.0005060889752501827</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.000214288117093268</v>
+        <v>0.0002168952751072212</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.003469768800195587</v>
+        <v>0.001880743452929848</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.001156589600065196</v>
+        <v>0.002731543183177291</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.001156589600065196</v>
+        <v>0.001170661364218839</v>
       </c>
     </row>
     <row r="43">
